--- a/July_2026_Farm_Report.xlsx
+++ b/July_2026_Farm_Report.xlsx
@@ -6,6 +6,8 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Requisitions" sheetId="2" r:id="rId2"/>
     <sheet name="Staff_Payroll" sheetId="3" r:id="rId3"/>
+    <sheet name="SACCO_Savings" sheetId="4" r:id="rId4"/>
+    <sheet name="SACCO_Repayments" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,15 +437,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Total July Expenses</v>
+        <v>Total July Farm Expenses</v>
       </c>
       <c r="B5" t="str">
         <v>UGX 13,189,250</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>July SACCO Savings Deposits</v>
+      </c>
+      <c r="B6" t="str">
+        <v>UGX 4,080,000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>July SACCO Loan Repayments Collected</v>
+      </c>
+      <c r="B7" t="str">
+        <v>UGX 950,000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1367,4 +1385,486 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C24"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Member</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Amount_UGX</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Kyarisiima Justus</v>
+      </c>
+      <c r="C3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Nayebare Prossy</v>
+      </c>
+      <c r="C4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Ainembabazi Queen</v>
+      </c>
+      <c r="C6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Kanyesigye immaculate</v>
+      </c>
+      <c r="C7">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Ainebyona Mebo</v>
+      </c>
+      <c r="C8">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Mzee Fred Kakombe</v>
+      </c>
+      <c r="C9">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mathias Twijukye</v>
+      </c>
+      <c r="C10">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Nyangoma Sharon</v>
+      </c>
+      <c r="C11">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C12">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Nimusiima Sharon</v>
+      </c>
+      <c r="C13">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Mathias Akampurira</v>
+      </c>
+      <c r="C14">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Fednand Tumusiime</v>
+      </c>
+      <c r="C15">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Simon Kulooba</v>
+      </c>
+      <c r="C16">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Frank Begumanya</v>
+      </c>
+      <c r="C17">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B18" t="str">
+        <v>muzahura  alex</v>
+      </c>
+      <c r="C18">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Amos</v>
+      </c>
+      <c r="C19">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Madam director</v>
+      </c>
+      <c r="C20">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Norman</v>
+      </c>
+      <c r="C21">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Elliot</v>
+      </c>
+      <c r="C22">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B23" t="str">
+        <v>jolly</v>
+      </c>
+      <c r="C23">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Frank  manager</v>
+      </c>
+      <c r="C24">
+        <v>100000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C24"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Member</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Loan_ID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Amount_UGX</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Ariho Micheal</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Nayebare Prossy</v>
+      </c>
+      <c r="C3">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sonia</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Kazoora Francis</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Mucunguzi Junior</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ainembabazi Queen</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Mathias Twijukye</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Nasasira Ainaea</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Nimusiima Sharon</v>
+      </c>
+      <c r="C10">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Fednand Tumusiime</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Simon Kulooba</v>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Frank Begumanya</v>
+      </c>
+      <c r="C13">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Norman</v>
+      </c>
+      <c r="C14">
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <v>30000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+  </ignoredErrors>
+</worksheet>
 </file>